--- a/hourly datasets/cap_gen_year16final.xlsx
+++ b/hourly datasets/cap_gen_year16final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1053331483093296</v>
+        <v>0.1023838315916107</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1136322875517179</v>
+        <v>0.1114590839502302</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2189654358610475</v>
+        <v>0.2138429155418409</v>
       </c>
     </row>
     <row r="4">
@@ -513,15 +513,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1024582439816771</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+        <v>0.09963553072547134</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.005701564153874888</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20.4948595639638</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.09215531584162896</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0884459145606131</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1108251468903305</v>
+      </c>
       <c r="H4" t="n">
-        <v>0.2077913922910067</v>
+        <v>0.202019362317082</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +541,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04180458250060327</v>
+        <v>0.03358409109010638</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -539,7 +549,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1471377308099329</v>
+        <v>0.1359679226817171</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +559,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02740139629355406</v>
+        <v>0.01825075998822561</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002515299710752093</v>
+        <v>0.001639521171315806</v>
       </c>
       <c r="D6" t="n">
-        <v>3.993518845385184</v>
+        <v>3.487930460392118</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01811784907453557</v>
+        <v>0.01629985896920962</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02246504313777602</v>
+        <v>0.01503191918092607</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03233774944933174</v>
+        <v>0.02146960079552533</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1327345446028836</v>
+        <v>0.1206345915798363</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +587,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01935738793585521</v>
+        <v>0.008715905353588007</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002275165851404394</v>
+        <v>0.001551086073550589</v>
       </c>
       <c r="D7" t="n">
-        <v>2.363449289881279</v>
+        <v>1.505694089577431</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04304667101166117</v>
+        <v>0.04060117177631738</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01489348645498139</v>
+        <v>0.005672028755964572</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02382128941672922</v>
+        <v>0.01175978195121136</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1246905362451848</v>
+        <v>0.1110997369451987</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +615,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01859274452294621</v>
+        <v>0.007595114727938585</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002034456734881975</v>
+        <v>0.001285936905956204</v>
       </c>
       <c r="D8" t="n">
-        <v>2.305548800137076</v>
+        <v>1.461741764628405</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0172915928024556</v>
+        <v>0.01281798704736675</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01459999903187738</v>
+        <v>0.005070214706823375</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02258549001401522</v>
+        <v>0.01012001474905412</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1239258928322758</v>
+        <v>0.1099789463195493</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +643,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01341835699473661</v>
+        <v>0.00123005122722035</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001917983871129994</v>
+        <v>0.001189016270954092</v>
       </c>
       <c r="D9" t="n">
-        <v>1.958452738426621</v>
+        <v>0.7530914704397229</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00580895883881699</v>
+        <v>0.002918394339849092</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009653782993790718</v>
+        <v>-0.001104873175449234</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0171829309956823</v>
+        <v>0.003564975629889958</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1187515053040662</v>
+        <v>0.103613882818831</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +671,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01500699362001514</v>
+        <v>0.002508552788240707</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002552263456055266</v>
+        <v>0.001756201157009433</v>
       </c>
       <c r="D10" t="n">
-        <v>2.12212481948439</v>
+        <v>0.9206015073218335</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00452888606977613</v>
+        <v>0.001718504500320617</v>
       </c>
       <c r="F10" t="n">
-        <v>0.009996370829102581</v>
+        <v>-0.0009410230420519047</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02001761641092765</v>
+        <v>0.005958128618533298</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1203401419293447</v>
+        <v>0.1048923843798514</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +699,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02943687797160316</v>
+        <v>0.02892687301130776</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +707,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1347700262809327</v>
+        <v>0.1313107046029185</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +717,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0540681740750615</v>
+        <v>0.05231408497268253</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +725,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1594013223843911</v>
+        <v>0.1546979165642932</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +735,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06931410665127544</v>
+        <v>0.06550073134814145</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +743,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.174647254960605</v>
+        <v>0.1678845629397522</v>
       </c>
     </row>
     <row r="14">
@@ -743,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07694405753430401</v>
+        <v>0.07355715630486687</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -751,7 +761,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1822772058436336</v>
+        <v>0.1759409878964776</v>
       </c>
     </row>
     <row r="15">
@@ -761,7 +771,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08434279519203611</v>
+        <v>0.08141285352743863</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -769,7 +779,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1896759435013657</v>
+        <v>0.1837966851190493</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +789,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.08793985650266503</v>
+        <v>0.0844457272204862</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -787,7 +797,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1932730048119946</v>
+        <v>0.1868295588120969</v>
       </c>
     </row>
     <row r="17">
@@ -797,7 +807,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.09051673174416253</v>
+        <v>0.08671132222721777</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -805,7 +815,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1958498800534921</v>
+        <v>0.1890951538188285</v>
       </c>
     </row>
     <row r="18">
@@ -815,7 +825,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1053331483093296</v>
+        <v>-0.1023838315916107</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -833,7 +843,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.09212893575831305</v>
+        <v>0.08922842208002044</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +851,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1974620840676426</v>
+        <v>0.1916122536716311</v>
       </c>
     </row>
     <row r="20">
@@ -851,7 +861,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09550757932538084</v>
+        <v>0.09250138886196198</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -859,7 +869,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.2008407276347104</v>
+        <v>0.1948852204535727</v>
       </c>
     </row>
     <row r="21">
@@ -869,7 +879,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1001145206728902</v>
+        <v>0.0968997860234571</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -877,7 +887,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.2054476689822198</v>
+        <v>0.1992836176150678</v>
       </c>
     </row>
     <row r="22">
@@ -887,25 +897,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1041123371286635</v>
+        <v>0.1018851301977097</v>
       </c>
       <c r="C22" t="n">
-        <v>0.006734902740321215</v>
+        <v>0.006592876323387853</v>
       </c>
       <c r="D22" t="n">
-        <v>235140220804.5638</v>
+        <v>232903597834.8295</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0321794941641154</v>
+        <v>0.03153258752515219</v>
       </c>
       <c r="F22" t="n">
-        <v>0.09088387040358084</v>
+        <v>0.08894094849643827</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1173408038537467</v>
+        <v>0.1148293118989814</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2094454854379931</v>
+        <v>0.2042689617893204</v>
       </c>
     </row>
     <row r="23">
@@ -915,25 +925,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1084776228961321</v>
+        <v>0.1061266721257273</v>
       </c>
       <c r="C23" t="n">
-        <v>0.006985265189092959</v>
+        <v>0.006691093057951022</v>
       </c>
       <c r="D23" t="n">
-        <v>359274961006.428</v>
+        <v>356950444604.1169</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03653729407134387</v>
+        <v>0.03603996214259708</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09475932487961147</v>
+        <v>0.09298499872536825</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1221959209126524</v>
+        <v>0.1192683455260857</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2138107712054617</v>
+        <v>0.208510503717338</v>
       </c>
     </row>
     <row r="24">
@@ -943,7 +953,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1114466841574084</v>
+        <v>0.1091661054396059</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -951,7 +961,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.2167798324667379</v>
+        <v>0.2115499370312166</v>
       </c>
     </row>
     <row r="25">
@@ -961,25 +971,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1130090738038105</v>
+        <v>0.110753084597976</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007274955822356711</v>
+        <v>0.007002711414772755</v>
       </c>
       <c r="D25" t="n">
-        <v>26.89075381159514</v>
+        <v>26.89987454440812</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04669545581823498</v>
+        <v>0.04584773656267969</v>
       </c>
       <c r="F25" t="n">
-        <v>0.09870644857410409</v>
+        <v>0.09699106289053329</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1273116990335168</v>
+        <v>0.1245151063054194</v>
       </c>
       <c r="H25" t="n">
-        <v>0.21834222211314</v>
+        <v>0.2131369161895867</v>
       </c>
     </row>
     <row r="26">
@@ -989,7 +999,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1158079375841897</v>
+        <v>0.1141260148058625</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
@@ -997,7 +1007,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0.2211410858935193</v>
+        <v>0.2165098463974732</v>
       </c>
     </row>
     <row r="27">
@@ -1007,25 +1017,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1209846171645378</v>
+        <v>0.1181989566402978</v>
       </c>
       <c r="C27" t="n">
-        <v>0.006979416414990986</v>
+        <v>0.006769209057760434</v>
       </c>
       <c r="D27" t="n">
-        <v>26.73276823934978</v>
+        <v>26.77889754153898</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05040596834229742</v>
+        <v>0.04982874570086933</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1072698523614101</v>
+        <v>0.1048949551740374</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1346993819676664</v>
+        <v>0.1315029581065583</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2263177654738673</v>
+        <v>0.2205827882319085</v>
       </c>
     </row>
     <row r="28">
@@ -1035,25 +1045,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1224983424820655</v>
+        <v>0.1203261121530779</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007210199647030541</v>
+        <v>0.006949083354225416</v>
       </c>
       <c r="D28" t="n">
-        <v>25.46995059647357</v>
+        <v>25.61855065569769</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08297233238895797</v>
+        <v>0.08334795958464968</v>
       </c>
       <c r="F28" t="n">
-        <v>0.108347778023142</v>
+        <v>0.1066862772856991</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1366489069409896</v>
+        <v>0.1339659470204572</v>
       </c>
       <c r="H28" t="n">
-        <v>0.227831490791395</v>
+        <v>0.2227099437446886</v>
       </c>
     </row>
     <row r="29">
@@ -1063,25 +1073,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.01972539771923136</v>
+        <v>0.006422193535711666</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001774406468956909</v>
+        <v>0.000947268811582631</v>
       </c>
       <c r="D29" t="n">
-        <v>2.822369345998223</v>
+        <v>1.49731139071211</v>
       </c>
       <c r="E29" t="n">
-        <v>0.06167796232882037</v>
+        <v>0.06498351658867454</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0162356048534354</v>
+        <v>0.004562400578529731</v>
       </c>
       <c r="G29" t="n">
-        <v>0.02321519058502691</v>
+        <v>0.008281986492893424</v>
       </c>
       <c r="H29" t="n">
-        <v>0.125058546028561</v>
+        <v>0.1088060251273224</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year16final.xlsx
+++ b/hourly datasets/cap_gen_year16final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2252322862547496</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1023838315916107</v>
+        <v>2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1014986231847647</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1114590839502302</v>
+        <v>0.3851596793498743</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.2138429155418409</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2614260162798894</v>
       </c>
     </row>
     <row r="4">
@@ -513,25 +524,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09963553072547134</v>
+        <v>0.419536588051285</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005701564153874888</v>
+        <v>0.006809376181261937</v>
       </c>
       <c r="D4" t="n">
-        <v>20.4948595639638</v>
+        <v>32.19345002064193</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09215531584162896</v>
+        <v>0.1011154181638333</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0884459145606131</v>
+        <v>0.1316660989710943</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1108251468903305</v>
+        <v>0.1583906251560825</v>
       </c>
       <c r="H4" t="n">
-        <v>0.202019362317082</v>
+        <v>8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2958029249813001</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +555,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03358409109010638</v>
+        <v>0.3717184241791183</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
@@ -549,7 +563,10 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>0.1359679226817171</v>
+        <v>23</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2479847611091334</v>
       </c>
     </row>
     <row r="6">
@@ -559,25 +576,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01825075998822561</v>
+        <v>0.3761780287574325</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001639521171315806</v>
+        <v>0.005858565899897764</v>
       </c>
       <c r="D6" t="n">
-        <v>3.487930460392118</v>
+        <v>4.741711492476718</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01629985896920962</v>
+        <v>0.1172664162243641</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01503191918092607</v>
+        <v>0.0139141448389627</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02146960079552533</v>
+        <v>0.03693785099898063</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1206345915798363</v>
+        <v>23</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2524443656874476</v>
       </c>
     </row>
     <row r="7">
@@ -587,25 +607,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008715905353588007</v>
+        <v>0.3711230703610817</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001551086073550589</v>
+        <v>0.006924812358970428</v>
       </c>
       <c r="D7" t="n">
-        <v>1.505694089577431</v>
+        <v>2.491998811961574</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04060117177631738</v>
+        <v>0.2823276372037633</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005672028755964572</v>
+        <v>0.001137195033474835</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01175978195121136</v>
+        <v>0.02834711516783111</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1110997369451987</v>
+        <v>23</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2473894072910968</v>
       </c>
     </row>
     <row r="8">
@@ -615,25 +638,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007595114727938585</v>
+        <v>0.3698665270183816</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001285936905956204</v>
+        <v>0.008281784560158911</v>
       </c>
       <c r="D8" t="n">
-        <v>1.461741764628405</v>
+        <v>2.868481572976448</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01281798704736675</v>
+        <v>0.1191051650059479</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005070214706823375</v>
+        <v>0.002475592993714999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01012001474905412</v>
+        <v>0.03502811353269538</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1099789463195493</v>
+        <v>23</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2461328639483967</v>
       </c>
     </row>
     <row r="9">
@@ -643,25 +669,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00123005122722035</v>
+        <v>0.3077734067877655</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001189016270954092</v>
+        <v>0.008768908754095204</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7530914704397229</v>
+        <v>-4.412008553877303</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002918394339849092</v>
+        <v>0.003035877413966326</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.001104873175449234</v>
+        <v>-0.06092338795319438</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003564975629889958</v>
+        <v>-0.02645465955326123</v>
       </c>
       <c r="H9" t="n">
-        <v>0.103613882818831</v>
+        <v>23</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1840397437177806</v>
       </c>
     </row>
     <row r="10">
@@ -671,25 +700,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002508552788240707</v>
+        <v>0.3150969545261356</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001756201157009433</v>
+        <v>0.01442012814214947</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9206015073218335</v>
+        <v>-1.654467696506823</v>
       </c>
       <c r="E10" t="n">
-        <v>0.001718504500320617</v>
+        <v>0.003887546505237921</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0009410230420519047</v>
+        <v>-0.06397196098149466</v>
       </c>
       <c r="G10" t="n">
-        <v>0.005958128618533298</v>
+        <v>-0.007286895794457625</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1048923843798514</v>
+        <v>23</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1913632914561507</v>
       </c>
     </row>
     <row r="11">
@@ -699,7 +731,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02892687301130776</v>
+        <v>0.273867457580895</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -707,7 +739,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1313107046029185</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1501337945109101</v>
       </c>
     </row>
     <row r="12">
@@ -717,7 +752,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05231408497268253</v>
+        <v>0.2997352624771121</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -725,7 +760,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1546979165642932</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1760015994071272</v>
       </c>
     </row>
     <row r="13">
@@ -735,7 +773,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.06550073134814145</v>
+        <v>0.3148057090399218</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -743,7 +781,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1678845629397522</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1910720459699369</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +794,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.07355715630486687</v>
+        <v>0.324480054297086</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -761,7 +802,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1759409878964776</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2007463912271011</v>
       </c>
     </row>
     <row r="15">
@@ -771,7 +815,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.08141285352743863</v>
+        <v>0.3332040586070205</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -779,7 +823,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1837966851190493</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2094703955370356</v>
       </c>
     </row>
     <row r="16">
@@ -789,7 +836,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0844457272204862</v>
+        <v>0.3369960555090245</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -797,7 +844,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1868295588120969</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2132623924390396</v>
       </c>
     </row>
     <row r="17">
@@ -807,7 +857,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.08671132222721777</v>
+        <v>0.3406476984745432</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
@@ -815,7 +865,10 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>0.1890951538188285</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.2169140354045583</v>
       </c>
     </row>
     <row r="18">
@@ -825,7 +878,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1023838315916107</v>
+        <v>0.1237336630699849</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
@@ -833,6 +886,9 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -843,7 +899,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.08922842208002044</v>
+        <v>0.3437328967974353</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -851,7 +907,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1916122536716311</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2199992337274504</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +920,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.09250138886196198</v>
+        <v>0.3463365077737577</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
@@ -869,7 +928,10 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.1948852204535727</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2226028447037728</v>
       </c>
     </row>
     <row r="21">
@@ -879,7 +941,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0968997860234571</v>
+        <v>0.35177125797302</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -887,7 +949,10 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.1992836176150678</v>
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2280375949030351</v>
       </c>
     </row>
     <row r="22">
@@ -897,25 +962,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1018851301977097</v>
+        <v>0.3568603324218556</v>
       </c>
       <c r="C22" t="n">
-        <v>0.006592876323387853</v>
+        <v>0.006588090701248423</v>
       </c>
       <c r="D22" t="n">
-        <v>232903597834.8295</v>
+        <v>232875486683.8202</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03153258752515219</v>
+        <v>0.03151771434558081</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08894094849643827</v>
+        <v>0.08887137560294063</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1148293118989814</v>
+        <v>0.1147409535912678</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2042689617893204</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2331266693518707</v>
       </c>
     </row>
     <row r="23">
@@ -925,25 +993,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1061266721257273</v>
+        <v>0.3632697830123517</v>
       </c>
       <c r="C23" t="n">
-        <v>0.006691093057951022</v>
+        <v>0.006686045433759186</v>
       </c>
       <c r="D23" t="n">
-        <v>356950444604.1169</v>
+        <v>356902173959.0672</v>
       </c>
       <c r="E23" t="n">
-        <v>0.03603996214259708</v>
+        <v>0.03601687938872044</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09298499872536825</v>
+        <v>0.09290426162070325</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1192683455260857</v>
+        <v>0.1191677929853073</v>
       </c>
       <c r="H23" t="n">
-        <v>0.208510503717338</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2395361199423668</v>
       </c>
     </row>
     <row r="24">
@@ -953,7 +1024,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1091661054396059</v>
+        <v>0.3673651643413884</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
@@ -961,7 +1032,10 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>0.2115499370312166</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2436315012714035</v>
       </c>
     </row>
     <row r="25">
@@ -971,25 +1045,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.110753084597976</v>
+        <v>0.371337550116438</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007002711414772755</v>
+        <v>0.006984847015336903</v>
       </c>
       <c r="D25" t="n">
-        <v>26.89987454440812</v>
+        <v>26.85778845671745</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04584773656267969</v>
+        <v>0.045682332798502</v>
       </c>
       <c r="F25" t="n">
-        <v>0.09699106289053329</v>
+        <v>0.09677804610540419</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1245151063054194</v>
+        <v>0.124231913669178</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2131369161895867</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2476038870464531</v>
       </c>
     </row>
     <row r="26">
@@ -999,7 +1076,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1141260148058625</v>
+        <v>0.3760464885313778</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
@@ -1007,7 +1084,10 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0.2165098463974732</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2523128254613929</v>
       </c>
     </row>
     <row r="27">
@@ -1017,25 +1097,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1181989566402978</v>
+        <v>0.3811893505232158</v>
       </c>
       <c r="C27" t="n">
-        <v>0.006769209057760434</v>
+        <v>0.006735889990721076</v>
       </c>
       <c r="D27" t="n">
-        <v>26.77889754153898</v>
+        <v>26.70011156310196</v>
       </c>
       <c r="E27" t="n">
-        <v>0.04982874570086933</v>
+        <v>0.04922097842216053</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1048949551740374</v>
+        <v>0.1044543382262146</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1315029581065583</v>
+        <v>0.1309314387081634</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2205827882319085</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2574556874532309</v>
       </c>
     </row>
     <row r="28">
@@ -1045,25 +1128,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1203261121530779</v>
+        <v>0.3862504560340928</v>
       </c>
       <c r="C28" t="n">
-        <v>0.006949083354225416</v>
+        <v>0.006878762569082412</v>
       </c>
       <c r="D28" t="n">
-        <v>25.61855065569769</v>
+        <v>25.45062080687169</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08334795958464968</v>
+        <v>0.08144814619682476</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1066862772856991</v>
+        <v>0.1056607523715163</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1339659470204572</v>
+        <v>0.1326642497298526</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2227099437446886</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2625167929641079</v>
       </c>
     </row>
     <row r="29">
@@ -1073,25 +1159,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.006422193535711666</v>
+        <v>0.3557290246697558</v>
       </c>
       <c r="C29" t="n">
-        <v>0.000947268811582631</v>
+        <v>0.005860102447390813</v>
       </c>
       <c r="D29" t="n">
-        <v>1.49731139071211</v>
+        <v>1.302651427232901</v>
       </c>
       <c r="E29" t="n">
-        <v>0.06498351658867454</v>
+        <v>0.7241389595028154</v>
       </c>
       <c r="F29" t="n">
-        <v>0.004562400578529731</v>
+        <v>-0.006191959922463176</v>
       </c>
       <c r="G29" t="n">
-        <v>0.008281986492893424</v>
+        <v>0.01684139526905468</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1088060251273224</v>
+        <v>23</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.2319953615997709</v>
       </c>
     </row>
   </sheetData>
